--- a/Analyses/mainStudy/01_dataPreperation/outputs/questionnaire/within_subjects/ques_study_within_vignettes.xlsx
+++ b/Analyses/mainStudy/01_dataPreperation/outputs/questionnaire/within_subjects/ques_study_within_vignettes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T15"/>
+  <dimension ref="A1:T57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -458,11 +458,11 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>bbbb</t>
+          <t>6a08b810d807f5805aabe02e</t>
         </is>
       </c>
       <c r="C2">
@@ -473,84 +473,84 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>anarchic</t>
+          <t>religious</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>anarchic</t>
+          <t>religious</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R2">
-        <v>32818</v>
+        <v>399052.5</v>
       </c>
       <c r="S2">
-        <v>32832</v>
+        <v>399058.058</v>
       </c>
       <c r="T2">
-        <v>32843</v>
+        <v>399058.058</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>bbbb</t>
+          <t>6a08b810d807f5805aabe02e</t>
         </is>
       </c>
       <c r="C3">
@@ -561,84 +561,84 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>aicentered</t>
+          <t>primitivist</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>aicentered</t>
+          <t>primitivist</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Q3">
         <v>0</v>
       </c>
       <c r="R3">
-        <v>55680</v>
+        <v>485900.5999999642</v>
       </c>
       <c r="S3">
-        <v>55691</v>
+        <v>485905.23</v>
       </c>
       <c r="T3">
-        <v>55704</v>
+        <v>485921.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>bbbb</t>
+          <t>6a08b810d807f5805aabe02e</t>
         </is>
       </c>
       <c r="C4">
@@ -659,74 +659,74 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Q4">
         <v>0</v>
       </c>
       <c r="R4">
-        <v>77475.00000000001</v>
+        <v>591297.6999999881</v>
       </c>
       <c r="S4">
-        <v>77486</v>
+        <v>591303.598</v>
       </c>
       <c r="T4">
-        <v>77498</v>
+        <v>591304.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>bbbb</t>
+          <t>6a08b810d807f5805aabe02e</t>
         </is>
       </c>
       <c r="C5">
@@ -737,84 +737,84 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>primitivist</t>
+          <t>anarchic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>primitivist</t>
+          <t>anarchic</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>107069</v>
+        <v>823172.8000000119</v>
       </c>
       <c r="S5">
-        <v>107081</v>
+        <v>823183.224</v>
       </c>
       <c r="T5">
-        <v>107095</v>
+        <v>823183.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>bbbb</t>
+          <t>6a08b810d807f5805aabe02e</t>
         </is>
       </c>
       <c r="C6">
@@ -825,84 +825,84 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>lawBased</t>
+          <t>futurist</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>lawBased</t>
+          <t>futurist</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Q6">
         <v>0</v>
       </c>
       <c r="R6">
-        <v>172396</v>
+        <v>950808</v>
       </c>
       <c r="S6">
-        <v>172408</v>
+        <v>950813.764</v>
       </c>
       <c r="T6">
-        <v>172419</v>
+        <v>950814.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>bbbb</t>
+          <t>6a08b810d807f5805aabe02e</t>
         </is>
       </c>
       <c r="C7">
@@ -913,84 +913,84 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>futurist</t>
+          <t>aicentered</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>futurist</t>
+          <t>aicentered</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q7">
         <v>0</v>
       </c>
       <c r="R7">
-        <v>194129</v>
+        <v>992931.5999999642</v>
       </c>
       <c r="S7">
-        <v>194140</v>
+        <v>992929.798</v>
       </c>
       <c r="T7">
-        <v>194153</v>
+        <v>992946.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>bbbb</t>
+          <t>6a08b810d807f5805aabe02e</t>
         </is>
       </c>
       <c r="C8">
@@ -1001,84 +1001,84 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>religious</t>
+          <t>lawBased</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>religious</t>
+          <t>lawBased</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8">
-        <v>217270</v>
+        <v>1042286</v>
       </c>
       <c r="S8">
-        <v>217282</v>
+        <v>1042279.866</v>
       </c>
       <c r="T8">
-        <v>217290</v>
+        <v>1042295.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>cc33</t>
+          <t>67103e4ed56cde03a0f2476b</t>
         </is>
       </c>
       <c r="C9">
@@ -1099,74 +1099,74 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Q9">
         <v>0</v>
       </c>
       <c r="R9">
-        <v>72615</v>
+        <v>579619</v>
       </c>
       <c r="S9">
-        <v>72631</v>
+        <v>579623.3320000001</v>
       </c>
       <c r="T9">
-        <v>72642</v>
+        <v>579623.3320000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>cc33</t>
+          <t>67103e4ed56cde03a0f2476b</t>
         </is>
       </c>
       <c r="C10">
@@ -1187,74 +1187,74 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q10">
         <v>0</v>
       </c>
       <c r="R10">
-        <v>97208</v>
+        <v>620408.5999999046</v>
       </c>
       <c r="S10">
-        <v>97221</v>
+        <v>620415.1</v>
       </c>
       <c r="T10">
-        <v>97235</v>
+        <v>620425.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>cc33</t>
+          <t>67103e4ed56cde03a0f2476b</t>
         </is>
       </c>
       <c r="C11">
@@ -1265,84 +1265,84 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>lawBased</t>
+          <t>aicentered</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>lawBased</t>
+          <t>aicentered</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q11">
         <v>0</v>
       </c>
       <c r="R11">
-        <v>121873</v>
+        <v>654098.5</v>
       </c>
       <c r="S11">
-        <v>121886</v>
+        <v>654097.7</v>
       </c>
       <c r="T11">
-        <v>121897</v>
+        <v>654107.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>cc33</t>
+          <t>67103e4ed56cde03a0f2476b</t>
         </is>
       </c>
       <c r="C12">
@@ -1353,84 +1353,84 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>aicentered</t>
+          <t>futurist</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>aicentered</t>
+          <t>futurist</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Q12">
         <v>0</v>
       </c>
       <c r="R12">
-        <v>149665</v>
+        <v>684372.8000001907</v>
       </c>
       <c r="S12">
-        <v>149677</v>
+        <v>684379</v>
       </c>
       <c r="T12">
-        <v>149684</v>
+        <v>684389</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>cc33</t>
+          <t>67103e4ed56cde03a0f2476b</t>
         </is>
       </c>
       <c r="C13">
@@ -1451,74 +1451,74 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R13">
-        <v>189186</v>
+        <v>714806.5</v>
       </c>
       <c r="S13">
-        <v>189197</v>
+        <v>714810.3</v>
       </c>
       <c r="T13">
-        <v>189213</v>
+        <v>714820.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>cc33</t>
+          <t>67103e4ed56cde03a0f2476b</t>
         </is>
       </c>
       <c r="C14">
@@ -1529,84 +1529,84 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>futurist</t>
+          <t>lawBased</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>futurist</t>
+          <t>lawBased</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R14">
-        <v>223851</v>
+        <v>783048.0999999046</v>
       </c>
       <c r="S14">
-        <v>223863</v>
+        <v>783055.7</v>
       </c>
       <c r="T14">
-        <v>223878</v>
+        <v>783065.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>cc33</t>
+          <t>67103e4ed56cde03a0f2476b</t>
         </is>
       </c>
       <c r="C15">
@@ -1627,65 +1627,3761 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Q15">
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <v>815140.5999999046</v>
+      </c>
+      <c r="S15">
+        <v>815147.7</v>
+      </c>
+      <c r="T15">
+        <v>815157.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>5</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>59a07638bfd73c00010ea394</t>
+        </is>
+      </c>
+      <c r="C16">
         <v>0</v>
       </c>
-      <c r="R15">
-        <v>277411</v>
-      </c>
-      <c r="S15">
-        <v>277423</v>
-      </c>
-      <c r="T15">
-        <v>277437</v>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>primitivist</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>primitivist</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <v>245894</v>
+      </c>
+      <c r="S16">
+        <v>245906.372</v>
+      </c>
+      <c r="T16">
+        <v>245906.4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>5</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>59a07638bfd73c00010ea394</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>anarchic</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>anarchic</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>337839.3000000119</v>
+      </c>
+      <c r="S17">
+        <v>337839.9</v>
+      </c>
+      <c r="T17">
+        <v>337853.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>5</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>59a07638bfd73c00010ea394</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>religious</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>religious</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q18">
+        <v>4</v>
+      </c>
+      <c r="R18">
+        <v>394047.099999994</v>
+      </c>
+      <c r="S18">
+        <v>394050.666</v>
+      </c>
+      <c r="T18">
+        <v>394060.6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>5</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>59a07638bfd73c00010ea394</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19">
+        <v>4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>lawBased</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>lawBased</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+      <c r="R19">
+        <v>441991</v>
+      </c>
+      <c r="S19">
+        <v>442000.6</v>
+      </c>
+      <c r="T19">
+        <v>442013.9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>5</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>59a07638bfd73c00010ea394</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20">
+        <v>5</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>aicentered</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>aicentered</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q20">
+        <v>1</v>
+      </c>
+      <c r="R20">
+        <v>496311.1999999881</v>
+      </c>
+      <c r="S20">
+        <v>496314.6</v>
+      </c>
+      <c r="T20">
+        <v>496327.9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>5</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>59a07638bfd73c00010ea394</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>5</v>
+      </c>
+      <c r="D21">
+        <v>6</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>futurist</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>futurist</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Q21">
+        <v>2</v>
+      </c>
+      <c r="R21">
+        <v>528217.1999999881</v>
+      </c>
+      <c r="S21">
+        <v>528216.466</v>
+      </c>
+      <c r="T21">
+        <v>528226.4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>5</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>59a07638bfd73c00010ea394</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>6</v>
+      </c>
+      <c r="D22">
+        <v>7</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>moderngreen</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>moderngreen</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>570270.900000006</v>
+      </c>
+      <c r="S22">
+        <v>570272.4</v>
+      </c>
+      <c r="T22">
+        <v>570285.7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>6</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>63d7b1a77e23b5460ab88069</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>religious</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>religious</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q23">
+        <v>2</v>
+      </c>
+      <c r="R23">
+        <v>263214.5</v>
+      </c>
+      <c r="S23">
+        <v>263223.266</v>
+      </c>
+      <c r="T23">
+        <v>263239.8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>6</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>63d7b1a77e23b5460ab88069</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>anarchic</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>anarchic</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q24">
+        <v>7</v>
+      </c>
+      <c r="R24">
+        <v>389497.900000006</v>
+      </c>
+      <c r="S24">
+        <v>389510.732</v>
+      </c>
+      <c r="T24">
+        <v>389527.4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>6</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>63d7b1a77e23b5460ab88069</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>aicentered</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>aicentered</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q25">
+        <v>2</v>
+      </c>
+      <c r="R25">
+        <v>493055.5</v>
+      </c>
+      <c r="S25">
+        <v>493064.2</v>
+      </c>
+      <c r="T25">
+        <v>493080.8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>6</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>63d7b1a77e23b5460ab88069</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+      <c r="D26">
+        <v>4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>lawBased</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>lawBased</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>544443.1000000015</v>
+      </c>
+      <c r="S26">
+        <v>544432.532</v>
+      </c>
+      <c r="T26">
+        <v>544449</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>6</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>63d7b1a77e23b5460ab88069</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>4</v>
+      </c>
+      <c r="D27">
+        <v>5</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>primitivist</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>primitivist</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>577571.3000000045</v>
+      </c>
+      <c r="S27">
+        <v>577567</v>
+      </c>
+      <c r="T27">
+        <v>577583.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>6</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>63d7b1a77e23b5460ab88069</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>5</v>
+      </c>
+      <c r="D28">
+        <v>6</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>futurist</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>futurist</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q28">
+        <v>2</v>
+      </c>
+      <c r="R28">
+        <v>714193.200000003</v>
+      </c>
+      <c r="S28">
+        <v>714204.73</v>
+      </c>
+      <c r="T28">
+        <v>714221.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>6</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>63d7b1a77e23b5460ab88069</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>6</v>
+      </c>
+      <c r="D29">
+        <v>7</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>moderngreen</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>moderngreen</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q29">
+        <v>1</v>
+      </c>
+      <c r="R29">
+        <v>818371.1000000015</v>
+      </c>
+      <c r="S29">
+        <v>818374.8639999999</v>
+      </c>
+      <c r="T29">
+        <v>818391.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>7</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>69c4160ec318cfcd7d4f37a4</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>anarchic</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>anarchic</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>469162.2000000477</v>
+      </c>
+      <c r="S30">
+        <v>469226.022</v>
+      </c>
+      <c r="T30">
+        <v>469226.022</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>7</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>69c4160ec318cfcd7d4f37a4</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>religious</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>religious</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q31">
+        <v>1</v>
+      </c>
+      <c r="R31">
+        <v>627108.8000000715</v>
+      </c>
+      <c r="S31">
+        <v>627112.478</v>
+      </c>
+      <c r="T31">
+        <v>627128.2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>7</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>69c4160ec318cfcd7d4f37a4</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+      <c r="D32">
+        <v>3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>lawBased</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>lawBased</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q32">
+        <v>2</v>
+      </c>
+      <c r="R32">
+        <v>752438.7000000477</v>
+      </c>
+      <c r="S32">
+        <v>752444.9300000001</v>
+      </c>
+      <c r="T32">
+        <v>752444.9300000001</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>7</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>69c4160ec318cfcd7d4f37a4</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>3</v>
+      </c>
+      <c r="D33">
+        <v>4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>futurist</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>futurist</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>847332.6000000238</v>
+      </c>
+      <c r="S33">
+        <v>847339.522</v>
+      </c>
+      <c r="T33">
+        <v>847339.522</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>7</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>69c4160ec318cfcd7d4f37a4</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>4</v>
+      </c>
+      <c r="D34">
+        <v>5</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>primitivist</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>primitivist</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>945841.8999999762</v>
+      </c>
+      <c r="S34">
+        <v>945848.1</v>
+      </c>
+      <c r="T34">
+        <v>945848.1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>7</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>69c4160ec318cfcd7d4f37a4</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>5</v>
+      </c>
+      <c r="D35">
+        <v>6</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>aicentered</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>aicentered</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>1040722</v>
+      </c>
+      <c r="S35">
+        <v>1040726.138</v>
+      </c>
+      <c r="T35">
+        <v>1040726.138</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>7</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>69c4160ec318cfcd7d4f37a4</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>6</v>
+      </c>
+      <c r="D36">
+        <v>7</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>moderngreen</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>moderngreen</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q36">
+        <v>1</v>
+      </c>
+      <c r="R36">
+        <v>1131438.300000072</v>
+      </c>
+      <c r="S36">
+        <v>1131442.346</v>
+      </c>
+      <c r="T36">
+        <v>1131442.346</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>8</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>69fe9e67a20599144f688b50</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>aicentered</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>aicentered</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>242278.6000001431</v>
+      </c>
+      <c r="S37">
+        <v>242279.362</v>
+      </c>
+      <c r="T37">
+        <v>242295.4</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>8</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>69fe9e67a20599144f688b50</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38">
+        <v>2</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>anarchic</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>anarchic</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q38">
+        <v>1</v>
+      </c>
+      <c r="R38">
+        <v>345346.4000000954</v>
+      </c>
+      <c r="S38">
+        <v>345340.03</v>
+      </c>
+      <c r="T38">
+        <v>345356.6</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>8</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>69fe9e67a20599144f688b50</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39">
+        <v>3</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>lawBased</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>lawBased</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>402731.2999999523</v>
+      </c>
+      <c r="S39">
+        <v>402737.466</v>
+      </c>
+      <c r="T39">
+        <v>402753.9</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>8</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>69fe9e67a20599144f688b50</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>3</v>
+      </c>
+      <c r="D40">
+        <v>4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>primitivist</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>primitivist</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <v>452587.7000000477</v>
+      </c>
+      <c r="S40">
+        <v>452584.8</v>
+      </c>
+      <c r="T40">
+        <v>452601.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>8</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>69fe9e67a20599144f688b50</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>4</v>
+      </c>
+      <c r="D41">
+        <v>5</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>futurist</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>futurist</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>504145.2999999523</v>
+      </c>
+      <c r="S41">
+        <v>504148.898</v>
+      </c>
+      <c r="T41">
+        <v>504165.2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>8</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>69fe9e67a20599144f688b50</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>5</v>
+      </c>
+      <c r="D42">
+        <v>6</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>moderngreen</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>moderngreen</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q42">
+        <v>3</v>
+      </c>
+      <c r="R42">
+        <v>535991</v>
+      </c>
+      <c r="S42">
+        <v>535997.1</v>
+      </c>
+      <c r="T42">
+        <v>536013.7</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>8</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>69fe9e67a20599144f688b50</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>6</v>
+      </c>
+      <c r="D43">
+        <v>7</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>religious</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>religious</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q43">
+        <v>1</v>
+      </c>
+      <c r="R43">
+        <v>572795.7999999523</v>
+      </c>
+      <c r="S43">
+        <v>572795.132</v>
+      </c>
+      <c r="T43">
+        <v>572811.7</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>9</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>69e91fd1a613772e648e565a</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>moderngreen</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>moderngreen</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>499003.2999999821</v>
+      </c>
+      <c r="S44">
+        <v>499027.862</v>
+      </c>
+      <c r="T44">
+        <v>499027.862</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>9</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>69e91fd1a613772e648e565a</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>2</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>primitivist</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>primitivist</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q45">
+        <v>2</v>
+      </c>
+      <c r="R45">
+        <v>604823.1999999881</v>
+      </c>
+      <c r="S45">
+        <v>604901.58</v>
+      </c>
+      <c r="T45">
+        <v>604901.58</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>9</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>69e91fd1a613772e648e565a</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
+      <c r="D46">
+        <v>3</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>religious</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>religious</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+      <c r="R46">
+        <v>713294.6999999881</v>
+      </c>
+      <c r="S46">
+        <v>713309.932</v>
+      </c>
+      <c r="T46">
+        <v>713309.932</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>9</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>69e91fd1a613772e648e565a</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>3</v>
+      </c>
+      <c r="D47">
+        <v>4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>futurist</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>futurist</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q47">
+        <v>2</v>
+      </c>
+      <c r="R47">
+        <v>755757.1999999881</v>
+      </c>
+      <c r="S47">
+        <v>755765.192</v>
+      </c>
+      <c r="T47">
+        <v>755781.5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>9</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>69e91fd1a613772e648e565a</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>4</v>
+      </c>
+      <c r="D48">
+        <v>5</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>anarchic</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>anarchic</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Q48">
+        <v>1</v>
+      </c>
+      <c r="R48">
+        <v>826040.6999999881</v>
+      </c>
+      <c r="S48">
+        <v>826043.122</v>
+      </c>
+      <c r="T48">
+        <v>826059.4</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>9</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>69e91fd1a613772e648e565a</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>5</v>
+      </c>
+      <c r="D49">
+        <v>6</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>lawBased</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>lawBased</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>873255.5</v>
+      </c>
+      <c r="S49">
+        <v>873261.752</v>
+      </c>
+      <c r="T49">
+        <v>873278</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>9</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>69e91fd1a613772e648e565a</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>6</v>
+      </c>
+      <c r="D50">
+        <v>7</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>aicentered</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>aicentered</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>912827.2999999821</v>
+      </c>
+      <c r="S50">
+        <v>912826.286</v>
+      </c>
+      <c r="T50">
+        <v>912842.3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>11</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>673e5fc42cbf961c153d09d3</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>futurist</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>futurist</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q51">
+        <v>1</v>
+      </c>
+      <c r="R51">
+        <v>168625.5</v>
+      </c>
+      <c r="S51">
+        <v>168632.824</v>
+      </c>
+      <c r="T51">
+        <v>168637.2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>11</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>673e5fc42cbf961c153d09d3</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <v>2</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>religious</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>religious</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="R52">
+        <v>259163</v>
+      </c>
+      <c r="S52">
+        <v>259165.73</v>
+      </c>
+      <c r="T52">
+        <v>259179.6</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>11</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>673e5fc42cbf961c153d09d3</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>2</v>
+      </c>
+      <c r="D53">
+        <v>3</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>moderngreen</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>moderngreen</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+      <c r="R53">
+        <v>332560.799999997</v>
+      </c>
+      <c r="S53">
+        <v>332565.8</v>
+      </c>
+      <c r="T53">
+        <v>332579.6</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>11</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>673e5fc42cbf961c153d09d3</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>3</v>
+      </c>
+      <c r="D54">
+        <v>4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>aicentered</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>aicentered</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q54">
+        <v>4</v>
+      </c>
+      <c r="R54">
+        <v>462740.299999997</v>
+      </c>
+      <c r="S54">
+        <v>462736.7</v>
+      </c>
+      <c r="T54">
+        <v>462750.5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>11</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>673e5fc42cbf961c153d09d3</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>4</v>
+      </c>
+      <c r="D55">
+        <v>5</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>primitivist</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>primitivist</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+      <c r="R55">
+        <v>622504</v>
+      </c>
+      <c r="S55">
+        <v>622504.63</v>
+      </c>
+      <c r="T55">
+        <v>622518.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>11</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>673e5fc42cbf961c153d09d3</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>5</v>
+      </c>
+      <c r="D56">
+        <v>6</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>lawBased</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>lawBased</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q56">
+        <v>1</v>
+      </c>
+      <c r="R56">
+        <v>672315.099999994</v>
+      </c>
+      <c r="S56">
+        <v>672319.1</v>
+      </c>
+      <c r="T56">
+        <v>672333</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>11</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>673e5fc42cbf961c153d09d3</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>6</v>
+      </c>
+      <c r="D57">
+        <v>7</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>anarchic</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>anarchic</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q57">
+        <v>2</v>
+      </c>
+      <c r="R57">
+        <v>710507.599999994</v>
+      </c>
+      <c r="S57">
+        <v>710514.6</v>
+      </c>
+      <c r="T57">
+        <v>710542.4</v>
       </c>
     </row>
   </sheetData>
